--- a/data/trans_dic/IP22_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,18; 25,9</t>
+          <t>14,85; 26,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 29,12</t>
+          <t>17,51; 30,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 26,18</t>
+          <t>14,78; 26,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,62; 24,02</t>
+          <t>12,6; 23,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 21,61</t>
+          <t>12,63; 22,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 31,66</t>
+          <t>19,07; 31,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 23,78</t>
+          <t>12,54; 24,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 22,67</t>
+          <t>9,72; 22,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,53; 21,78</t>
+          <t>14,63; 21,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 28,29</t>
+          <t>19,97; 28,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 23,14</t>
+          <t>15,3; 23,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 21,04</t>
+          <t>12,35; 20,68</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,03; 24,62</t>
+          <t>16,24; 24,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,33; 34,25</t>
+          <t>24,13; 34,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 23,03</t>
+          <t>14,63; 23,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,85; 29,04</t>
+          <t>14,67; 28,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,02; 31,87</t>
+          <t>21,79; 31,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,91; 32,74</t>
+          <t>22,39; 32,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 19,87</t>
+          <t>12,44; 19,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 17,52</t>
+          <t>9,6; 17,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,67; 27,35</t>
+          <t>20,31; 27,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,62; 31,93</t>
+          <t>24,69; 31,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 20,18</t>
+          <t>14,43; 20,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 20,46</t>
+          <t>12,94; 20,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 32,5</t>
+          <t>21,15; 33,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,11; 26,76</t>
+          <t>16,05; 26,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 27,41</t>
+          <t>17,15; 28,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 20,1</t>
+          <t>8,69; 19,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,08; 32,93</t>
+          <t>20,95; 32,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,04; 43,3</t>
+          <t>30,83; 43,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 24,44</t>
+          <t>14,82; 24,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,6</t>
+          <t>10,43; 20,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 30,58</t>
+          <t>22,28; 30,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 33,51</t>
+          <t>25,69; 33,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,19</t>
+          <t>17,55; 24,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 18,36</t>
+          <t>10,58; 18,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,07</t>
+          <t>9,51; 17,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 24,95</t>
+          <t>15,88; 25,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,08</t>
+          <t>8,42; 15,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 16,77</t>
+          <t>7,27; 15,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,15; 21,46</t>
+          <t>12,89; 21,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,8</t>
+          <t>17,36; 27,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 19,43</t>
+          <t>11,03; 19,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 25,08</t>
+          <t>14,58; 25,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 18,27</t>
+          <t>12,06; 18,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 24,94</t>
+          <t>17,76; 24,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,46</t>
+          <t>10,82; 16,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,32</t>
+          <t>11,95; 18,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,77</t>
+          <t>16,86; 21,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,33</t>
+          <t>20,83; 26,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 20,33</t>
+          <t>15,42; 19,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,64</t>
+          <t>12,64; 18,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 24,25</t>
+          <t>19,37; 24,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,97; 30,5</t>
+          <t>24,91; 30,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 19,17</t>
+          <t>14,55; 19,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,08; 18,11</t>
+          <t>13,07; 17,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 22,22</t>
+          <t>18,82; 22,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,74; 27,66</t>
+          <t>23,84; 27,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,87</t>
+          <t>15,48; 18,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,75; 17,63</t>
+          <t>13,63; 17,65</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21059; 35930</t>
+          <t>20602; 36284</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24437; 40584</t>
+          <t>24399; 41956</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19365; 35009</t>
+          <t>19767; 34936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14804; 28170</t>
+          <t>14778; 28001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18537; 33078</t>
+          <t>19327; 34285</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28969; 48969</t>
+          <t>29494; 48092</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18589; 35207</t>
+          <t>18576; 36042</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13287; 31830</t>
+          <t>13643; 31505</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42408; 63555</t>
+          <t>42693; 63912</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58099; 83192</t>
+          <t>58713; 84012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42126; 65203</t>
+          <t>43110; 65433</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31947; 54210</t>
+          <t>31820; 53279</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31276; 48051</t>
+          <t>31693; 48748</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50060; 70461</t>
+          <t>49646; 70739</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30208; 47737</t>
+          <t>30329; 47998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28293; 55319</t>
+          <t>27956; 54180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46707; 67600</t>
+          <t>46217; 65940</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51123; 73057</t>
+          <t>49972; 72469</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26409; 44570</t>
+          <t>27917; 44761</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24860; 44677</t>
+          <t>24494; 44119</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84205; 111381</t>
+          <t>82722; 110499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105593; 136945</t>
+          <t>105879; 136846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62532; 87109</t>
+          <t>62296; 87699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57744; 91167</t>
+          <t>57640; 91041</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28736; 44789</t>
+          <t>29147; 45871</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25023; 41584</t>
+          <t>24940; 40629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26368; 42755</t>
+          <t>26755; 43757</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15721; 38102</t>
+          <t>16483; 37637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31541; 49288</t>
+          <t>31359; 47981</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51163; 71380</t>
+          <t>50829; 71109</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24360; 40728</t>
+          <t>24704; 41257</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18933; 38164</t>
+          <t>19320; 38374</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63232; 87917</t>
+          <t>64046; 88315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80692; 107296</t>
+          <t>82261; 107288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56173; 78044</t>
+          <t>56637; 79168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40378; 68829</t>
+          <t>39671; 70361</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20051; 37825</t>
+          <t>19904; 36772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32513; 52480</t>
+          <t>33388; 53617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17300; 33346</t>
+          <t>17466; 33021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12019; 28040</t>
+          <t>12154; 26729</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27339; 44604</t>
+          <t>26782; 44403</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36546; 55646</t>
+          <t>36051; 56868</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22358; 39806</t>
+          <t>22595; 39849</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26592; 45457</t>
+          <t>26417; 45578</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52409; 76206</t>
+          <t>50307; 75475</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73648; 104228</t>
+          <t>74215; 103016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44505; 67884</t>
+          <t>44603; 68297</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40824; 67341</t>
+          <t>41645; 65332</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114820; 148284</t>
+          <t>114811; 148370</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>149607; 187162</t>
+          <t>148063; 187006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109625; 143203</t>
+          <t>108595; 140126</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84455; 123880</t>
+          <t>84008; 124638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>139843; 175288</t>
+          <t>140014; 175099</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187350; 228833</t>
+          <t>186934; 227835</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108303; 142659</t>
+          <t>108277; 141691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99644; 138030</t>
+          <t>99617; 135313</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>264539; 311881</t>
+          <t>264161; 315664</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346823; 404113</t>
+          <t>348333; 403716</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227897; 273282</t>
+          <t>224244; 271598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>196171; 251523</t>
+          <t>194422; 251730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP22_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP22_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24,87%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,81%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,48%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 26,16</t>
+          <t>12,42; 21,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,51; 30,11</t>
+          <t>19,27; 31,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 26,13</t>
+          <t>12,93; 23,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 23,87</t>
+          <t>9,9; 22,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 22,4</t>
+          <t>14,9; 25,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 31,09</t>
+          <t>17,63; 30,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 24,34</t>
+          <t>14,59; 25,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 22,44</t>
+          <t>11,78; 23,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 21,9</t>
+          <t>14,69; 22,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 28,57</t>
+          <t>20,01; 28,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,3; 23,22</t>
+          <t>15,26; 22,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 20,68</t>
+          <t>11,97; 20,54</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>29,04%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>18,57%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,98</t>
+          <t>21,76; 31,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,13; 34,39</t>
+          <t>22,16; 32,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 23,16</t>
+          <t>12,34; 19,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,67; 28,44</t>
+          <t>9,54; 17,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,79; 31,08</t>
+          <t>16,06; 25,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,39; 32,47</t>
+          <t>24,56; 34,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 19,95</t>
+          <t>14,59; 22,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,3</t>
+          <t>12,56; 22,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,31; 27,13</t>
+          <t>20,45; 27,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,69; 31,91</t>
+          <t>24,65; 31,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 20,32</t>
+          <t>14,08; 20,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,94; 20,43</t>
+          <t>11,72; 17,94</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>26,13%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>21,15%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>21,98%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,15; 33,28</t>
+          <t>20,73; 32,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,05; 26,15</t>
+          <t>31,13; 42,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,15; 28,05</t>
+          <t>15,06; 24,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,85</t>
+          <t>10,48; 21,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,95; 32,06</t>
+          <t>20,64; 31,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,83; 43,14</t>
+          <t>15,78; 26,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,82; 24,75</t>
+          <t>17,22; 27,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 20,71</t>
+          <t>13,4; 24,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,28; 30,72</t>
+          <t>22,62; 30,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 33,5</t>
+          <t>25,6; 33,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,55; 24,54</t>
+          <t>17,27; 24,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 18,77</t>
+          <t>13,14; 20,42</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,36%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 17,57</t>
+          <t>13,26; 21,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 25,5</t>
+          <t>17,43; 26,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,92</t>
+          <t>10,85; 19,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 15,98</t>
+          <t>13,77; 23,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 21,37</t>
+          <t>9,6; 17,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,36; 27,39</t>
+          <t>16,17; 25,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,45</t>
+          <t>8,71; 16,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,58; 25,15</t>
+          <t>6,38; 13,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 18,09</t>
+          <t>12,63; 18,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,76; 24,65</t>
+          <t>17,85; 24,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,56</t>
+          <t>10,58; 16,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 18,75</t>
+          <t>11,06; 17,48</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,86; 21,79</t>
+          <t>19,2; 24,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,83; 26,31</t>
+          <t>25,01; 30,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 19,89</t>
+          <t>14,51; 19,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 18,75</t>
+          <t>12,93; 17,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 24,23</t>
+          <t>17,06; 21,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,91; 30,36</t>
+          <t>21,26; 26,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 19,04</t>
+          <t>15,45; 19,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,76</t>
+          <t>12,96; 17,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 22,49</t>
+          <t>18,8; 22,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,84; 27,63</t>
+          <t>23,92; 27,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 18,75</t>
+          <t>15,63; 18,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,65</t>
+          <t>13,28; 17,05</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25561</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38472</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>27747</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>32719</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>26664</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20629</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25561</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38472</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41797</t>
+          <t>39080</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20602; 36284</t>
+          <t>19013; 33631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24399; 41956</t>
+          <t>29804; 48445</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19767; 34936</t>
+          <t>19151; 35371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14778; 28001</t>
+          <t>12469; 27896</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19327; 34285</t>
+          <t>20663; 36045</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29494; 48092</t>
+          <t>24566; 43184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18576; 36042</t>
+          <t>19504; 34190</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13643; 31505</t>
+          <t>14266; 28048</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42693; 63912</t>
+          <t>42865; 64858</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58713; 84012</t>
+          <t>58844; 83545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43110; 65433</t>
+          <t>42994; 64434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31820; 53279</t>
+          <t>29558; 50728</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56672</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61684</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35250</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30355</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>39951</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>59736</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38477</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37667</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56672</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61684</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35250</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33358</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>61836</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31693; 48748</t>
+          <t>46159; 66731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49646; 70739</t>
+          <t>49460; 72932</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30329; 47998</t>
+          <t>27690; 44502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27956; 54180</t>
+          <t>22633; 41294</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46217; 65940</t>
+          <t>31338; 49068</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49972; 72469</t>
+          <t>50523; 70812</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27917; 44761</t>
+          <t>30244; 47452</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24494; 44119</t>
+          <t>23159; 40591</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82722; 110499</t>
+          <t>83301; 110255</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>105879; 136846</t>
+          <t>105721; 136694</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62296; 87699</t>
+          <t>60771; 87068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57640; 91041</t>
+          <t>49412; 75640</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39478</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60934</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25337</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>36008</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>32862</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>34286</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26895</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>39478</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60934</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32409</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54569</t>
+          <t>53247</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29147; 45871</t>
+          <t>31020; 48545</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24940; 40629</t>
+          <t>51325; 70692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26755; 43757</t>
+          <t>25105; 41229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16483; 37637</t>
+          <t>17646; 35882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31359; 47981</t>
+          <t>28441; 43934</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50829; 71109</t>
+          <t>24526; 40985</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24704; 41257</t>
+          <t>26866; 42503</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19320; 38374</t>
+          <t>20930; 38141</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64046; 88315</t>
+          <t>65030; 87265</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82261; 107288</t>
+          <t>81977; 107808</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56637; 79168</t>
+          <t>55718; 79646</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39671; 70361</t>
+          <t>42642; 66261</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35318</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45727</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30499</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31117</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>27955</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>42501</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>24657</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18045</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35318</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45727</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30499</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>47247</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19904; 36772</t>
+          <t>27561; 44922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33388; 53617</t>
+          <t>36187; 55146</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17466; 33021</t>
+          <t>22232; 39551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12154; 26729</t>
+          <t>23322; 40198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26782; 44403</t>
+          <t>20085; 37329</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36051; 56868</t>
+          <t>34007; 54457</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22595; 39849</t>
+          <t>18075; 33239</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26417; 45578</t>
+          <t>10617; 22821</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50307; 75475</t>
+          <t>52690; 75923</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74215; 103016</t>
+          <t>74613; 104073</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44603; 68297</t>
+          <t>43608; 66073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41645; 65332</t>
+          <t>37143; 58689</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114811; 148370</t>
+          <t>138749; 177154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148063; 187006</t>
+          <t>187656; 230418</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108595; 140126</t>
+          <t>107955; 142338</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84008; 124638</t>
+          <t>90588; 125160</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>140014; 175099</t>
+          <t>116201; 149172</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>186934; 227835</t>
+          <t>151095; 186466</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108277; 141691</t>
+          <t>108859; 140183</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99617; 135313</t>
+          <t>81393; 111298</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>264161; 315664</t>
+          <t>263954; 313393</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348333; 403716</t>
+          <t>349557; 404110</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>224244; 271598</t>
+          <t>226452; 272633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>194422; 251730</t>
+          <t>176479; 226552</t>
         </is>
       </c>
     </row>
